--- a/analysis/aggregate/generative.xlsx
+++ b/analysis/aggregate/generative.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK9"/>
+  <dimension ref="A1:AK17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,7 +611,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -638,22 +638,22 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8320738773917988</v>
+        <v>0.8273050431713951</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01009202567273346</v>
+        <v>0.001359001240486718</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9860746807074998</v>
+        <v>0.9872337263398052</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01323605724407899</v>
+        <v>0.01267520072742623</v>
       </c>
       <c r="L2" t="n">
-        <v>0.996792550439731</v>
+        <v>0.9901707190894982</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02729231366164868</v>
+        <v>0.01610386178610805</v>
       </c>
       <c r="N2" t="n">
         <v>1933</v>
@@ -662,70 +662,70 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1926.8</v>
+        <v>1914</v>
       </c>
       <c r="Q2" t="n">
-        <v>52.75604230796696</v>
+        <v>31.12876483254676</v>
       </c>
       <c r="R2" t="n">
-        <v>0.912556143306958</v>
+        <v>0.9092920270213792</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0173956213179226</v>
+        <v>0.007513307439838513</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8617358983769104</v>
+        <v>0.8568997395190447</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01848491181618573</v>
+        <v>0.008916819924062703</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8204781933375118</v>
+        <v>0.8139163539932989</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02041860815145606</v>
+        <v>0.01078799855945918</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7865687342903215</v>
+        <v>0.7780001021324648</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.02365482685707256</v>
+        <v>0.01121872197866065</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.9220854327084155</v>
+        <v>0.9142593844753788</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.005546661398221416</v>
+        <v>0.003530232510772202</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9274851707550251</v>
+        <v>0.9206323233498352</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.005118336229047927</v>
+        <v>0.001177386710212972</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.8750759052686956</v>
+        <v>0.8665283297092273</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.01168772652928395</v>
+        <v>0.005488937729954532</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.9160836170272886</v>
+        <v>0.9056319126364961</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.009607846144815435</v>
+        <v>0.002998075147592713</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.9157580748900053</v>
+        <v>0.9058122432164868</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.00968321174760846</v>
+        <v>0.003523880918820118</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1486002239641657</v>
+        <v>0.1645776566757493</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.01454474402384382</v>
+        <v>0.004687915676862473</v>
       </c>
     </row>
     <row r="3">
@@ -736,7 +736,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -763,22 +763,22 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8320738773917988</v>
+        <v>0.7450522073408006</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01009202567273346</v>
+        <v>0.08822614134945737</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9860746807074998</v>
+        <v>0.998858628268712</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01323605724407899</v>
+        <v>0.002552184778756518</v>
       </c>
       <c r="L3" t="n">
-        <v>0.996792550439731</v>
+        <v>1.069218830832902</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02729231366164868</v>
+        <v>0.1393682229968414</v>
       </c>
       <c r="N3" t="n">
         <v>1933</v>
@@ -787,70 +787,70 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1926.8</v>
+        <v>2066.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>52.75604230796696</v>
+        <v>269.3987750528945</v>
       </c>
       <c r="R3" t="n">
-        <v>0.912556143306958</v>
+        <v>0.8198353862422942</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0173956213179226</v>
+        <v>0.09213705341683857</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8617358983769104</v>
+        <v>0.7650798905192053</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01848491181618573</v>
+        <v>0.08867937435664459</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8204781933375118</v>
+        <v>0.7208009298746269</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02041860815145606</v>
+        <v>0.08692992720120768</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7865687342903215</v>
+        <v>0.6848953933455436</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02365482685707256</v>
+        <v>0.08696622961631495</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.9220854327084155</v>
+        <v>0.8848227512444622</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005546661398221416</v>
+        <v>0.00851676324074924</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9274851707550251</v>
+        <v>0.8883611644077352</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.005118336229047927</v>
+        <v>0.006713807418121349</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.8750759052686956</v>
+        <v>0.832167664249025</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.01168772652928395</v>
+        <v>0.005528753652546485</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.9160836170272886</v>
+        <v>0.8772194507083941</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.009607846144815435</v>
+        <v>0.006673609034999576</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9157580748900053</v>
+        <v>0.8771118075857924</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.00968321174760846</v>
+        <v>0.007132392395928331</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1901907356948229</v>
+        <v>0.300708446866485</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01449529817795137</v>
+        <v>0.1505638342440073</v>
       </c>
     </row>
     <row r="4">
@@ -861,7 +861,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -888,22 +888,22 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8109046280008465</v>
+        <v>0.7414734126140788</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02704788241368848</v>
+        <v>0.08516716281816633</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9971868140997477</v>
+        <v>0.9966699471786515</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006290474906307882</v>
+        <v>0.005864927705790115</v>
       </c>
       <c r="L4" t="n">
-        <v>1.027521986549405</v>
+        <v>1.111226073460941</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03561211388012747</v>
+        <v>0.1190838348355368</v>
       </c>
       <c r="N4" t="n">
         <v>1933</v>
@@ -912,70 +912,70 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1986.2</v>
+        <v>2148</v>
       </c>
       <c r="Q4" t="n">
-        <v>68.83821613028623</v>
+        <v>230.1890527370926</v>
       </c>
       <c r="R4" t="n">
-        <v>0.879995163970678</v>
+        <v>0.8162152670624769</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03116160060338253</v>
+        <v>0.08936555044892601</v>
       </c>
       <c r="T4" t="n">
-        <v>0.830680850478695</v>
+        <v>0.7638228301397516</v>
       </c>
       <c r="U4" t="n">
-        <v>0.029921247735824</v>
+        <v>0.08761801795640609</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7904798347607052</v>
+        <v>0.7203569661370154</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02953122084704332</v>
+        <v>0.08856151321571945</v>
       </c>
       <c r="X4" t="n">
-        <v>0.757148184514677</v>
+        <v>0.683360724197301</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03008388101686572</v>
+        <v>0.08970778560051847</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.9129169593357778</v>
+        <v>0.9058587892913437</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.005549560857646939</v>
+        <v>0.003270465643860577</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9185022820772157</v>
+        <v>0.9120778912904985</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.005077558463907992</v>
+        <v>0.004847917413308645</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.8657745078763934</v>
+        <v>0.8560359647917398</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.003682233818069536</v>
+        <v>0.008777597652145013</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.9077276191206274</v>
+        <v>0.8956666692736548</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.003603504582639035</v>
+        <v>0.003499724430312057</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.9076580813565027</v>
+        <v>0.8952761436987966</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.004136877555336368</v>
+        <v>0.003811408397708238</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.1927211646136618</v>
+        <v>0.2974386920980926</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.04297727327309011</v>
+        <v>0.122899701614933</v>
       </c>
     </row>
     <row r="5">
@@ -986,7 +986,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1013,22 +1013,22 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8109046280008465</v>
+        <v>0.5931048379085917</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02704788241368848</v>
+        <v>0.1040777911348678</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9971868140997477</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006290474906307882</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.027521986549405</v>
+        <v>1.327263321262287</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03561211388012747</v>
+        <v>0.1863261421727778</v>
       </c>
       <c r="N5" t="n">
         <v>1933</v>
@@ -1037,70 +1037,70 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1986.2</v>
+        <v>2565.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>68.83821613028623</v>
+        <v>360.1684328199794</v>
       </c>
       <c r="R5" t="n">
-        <v>0.879995163970678</v>
+        <v>0.6647619596005004</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03116160060338253</v>
+        <v>0.1092326906763957</v>
       </c>
       <c r="T5" t="n">
-        <v>0.830680850478695</v>
+        <v>0.6128835134007172</v>
       </c>
       <c r="U5" t="n">
-        <v>0.029921247735824</v>
+        <v>0.1046442583410037</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7904798347607052</v>
+        <v>0.5694837978844337</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02953122084704332</v>
+        <v>0.1017689152726394</v>
       </c>
       <c r="X5" t="n">
-        <v>0.757148184514677</v>
+        <v>0.5334102651105512</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03008388101686572</v>
+        <v>0.1004580910478371</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9129169593357778</v>
+        <v>0.8730149123517306</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005549560857646939</v>
+        <v>0.004256074176362457</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9185022820772157</v>
+        <v>0.8751195797987081</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.005077558463907992</v>
+        <v>0.005736440199221121</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.8657745078763934</v>
+        <v>0.8183687234831118</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.003682233818069536</v>
+        <v>0.007457000263668703</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.9077276191206274</v>
+        <v>0.8632866885403701</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.003603504582639035</v>
+        <v>0.005313885205157843</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.9076580813565027</v>
+        <v>0.8627470325682547</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.004136877555336368</v>
+        <v>0.006129075686788877</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2323705722070844</v>
+        <v>0.5740599455040872</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.04136954126566399</v>
+        <v>0.1921317534811748</v>
       </c>
     </row>
     <row r="6">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1135,25 +1135,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8250557353750306</v>
+        <v>0.8115676584375976</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0108734106249245</v>
+        <v>0.0106426093157776</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9882611329385342</v>
+        <v>0.9719346695365931</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01955781620400904</v>
+        <v>0.0172217002678691</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9886051619989017</v>
+        <v>0.9724327292696321</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01926656891498832</v>
+        <v>0.01668093209804034</v>
       </c>
       <c r="N6" t="n">
         <v>1821</v>
@@ -1162,70 +1162,70 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1800.25</v>
+        <v>1770.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>35.08442199419378</v>
+        <v>30.37597735053145</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9059766344845758</v>
+        <v>0.9088499987062149</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009287812376401347</v>
+        <v>0.009478603631717965</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8531646788384718</v>
+        <v>0.8541556997567602</v>
       </c>
       <c r="U6" t="n">
-        <v>0.008133792415239963</v>
+        <v>0.01069517908374172</v>
       </c>
       <c r="V6" t="n">
-        <v>0.813520449069688</v>
+        <v>0.8125478518170303</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008863268746724388</v>
+        <v>0.01346982386077339</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7729454836544</v>
+        <v>0.7711799997827675</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009516599464614892</v>
+        <v>0.01731052085004423</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9137960132340278</v>
+        <v>0.9055050340135764</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003222770662101531</v>
+        <v>0.00514980577380493</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9279756575866204</v>
+        <v>0.9236217315105855</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.002726006589007379</v>
+        <v>0.00325521436228356</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.8863700984542131</v>
+        <v>0.8785295698344179</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.001736331372792155</v>
+        <v>0.004782441792097627</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.9237485387686368</v>
+        <v>0.9180661053828171</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.002137550009921369</v>
+        <v>0.002290486151917888</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.9234456618158194</v>
+        <v>0.9183449255894287</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.001876348927294145</v>
+        <v>0.002857883711751393</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1579264617239301</v>
+        <v>0.1617046117921775</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.003843907267371714</v>
+        <v>0.006094749859258926</v>
       </c>
     </row>
     <row r="7">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1263,22 +1263,22 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8247626307860454</v>
+        <v>0.8115676584375976</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009439430356969971</v>
+        <v>0.0106426093157776</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9906089063508274</v>
+        <v>0.9719346695365931</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01773249364809425</v>
+        <v>0.0172217002678691</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9935200439319056</v>
+        <v>0.9724327292696321</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01997951026411396</v>
+        <v>0.01668093209804034</v>
       </c>
       <c r="N7" t="n">
         <v>1821</v>
@@ -1287,70 +1287,70 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1809.2</v>
+        <v>1770.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>36.38268819095148</v>
+        <v>30.37597735053145</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9035346951215359</v>
+        <v>0.9088499987062149</v>
       </c>
       <c r="S7" t="n">
-        <v>0.009721776242963135</v>
+        <v>0.009478603631717965</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8503971723051162</v>
+        <v>0.8541556997567602</v>
       </c>
       <c r="U7" t="n">
-        <v>0.009376267719700286</v>
+        <v>0.01069517908374172</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8112655170848209</v>
+        <v>0.8125478518170303</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009183775963043664</v>
+        <v>0.01346982386077339</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7712578714039517</v>
+        <v>0.7711799997827675</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.009064459419443846</v>
+        <v>0.01731052085004423</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.913551651037633</v>
+        <v>0.9055050340135764</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002843985314749591</v>
+        <v>0.00514980577380493</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9271125527039052</v>
+        <v>0.9236217315105855</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.003049276001826901</v>
+        <v>0.00325521436228356</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.8843957665518658</v>
+        <v>0.8785295698344179</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.004663803949593002</v>
+        <v>0.004782441792097627</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.9223744675285264</v>
+        <v>0.9180661053828171</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.00358708780184999</v>
+        <v>0.002290486151917888</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.9222233944121946</v>
+        <v>0.9183449255894287</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.003179654384133185</v>
+        <v>0.002857883711751393</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.2037361354349095</v>
+        <v>0.1617046117921775</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.00580844972041226</v>
+        <v>0.006094749859258926</v>
       </c>
     </row>
     <row r="8">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1388,22 +1388,22 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8192814030233995</v>
+        <v>0.7250156239711663</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01247648848990439</v>
+        <v>0.0695254530698281</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9819125624292745</v>
+        <v>0.9966778178954613</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0252031656696641</v>
+        <v>0.007428625019381896</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9938495332235036</v>
+        <v>1.123448654585393</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03726208433699708</v>
+        <v>0.1119519032002793</v>
       </c>
       <c r="N8" t="n">
         <v>1821</v>
@@ -1412,70 +1412,70 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1809.8</v>
+        <v>2045.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>67.85425557767176</v>
+        <v>203.8644157277086</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9005913783012467</v>
+        <v>0.7965712665878296</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02943620063723383</v>
+        <v>0.07410462791762003</v>
       </c>
       <c r="T8" t="n">
-        <v>0.850900853631449</v>
+        <v>0.7453379467010517</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0287185593420482</v>
+        <v>0.07299534777483786</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8146661846747735</v>
+        <v>0.7070288067548065</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02969977673458377</v>
+        <v>0.07383407280347484</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7784665883757202</v>
+        <v>0.6683757210654035</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03088965888839629</v>
+        <v>0.07535880398930604</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9104244512717476</v>
+        <v>0.8956676568094991</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.007556337329172617</v>
+        <v>0.003876439338451216</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9258008696292567</v>
+        <v>0.908889127474934</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.00581648641956653</v>
+        <v>0.006880777454275891</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.8823264772716908</v>
+        <v>0.863632373031453</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.007233991165855591</v>
+        <v>0.007821318699022049</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.9212422337195283</v>
+        <v>0.9047695926059749</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.006524887031671313</v>
+        <v>0.00625828988828591</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.9212780377096174</v>
+        <v>0.9045095890677143</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.006273841921794771</v>
+        <v>0.006327084922052311</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.1731163351416516</v>
+        <v>0.3053123175715119</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.03293368523889948</v>
+        <v>0.09944092378187683</v>
       </c>
     </row>
     <row r="9">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1513,22 +1513,22 @@
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8192814030233995</v>
+        <v>0.7250156239711663</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01247648848990439</v>
+        <v>0.0695254530698281</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9819125624292745</v>
+        <v>0.9966778178954613</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0252031656696641</v>
+        <v>0.007428625019381896</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9938495332235036</v>
+        <v>1.123448654585393</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03726208433699708</v>
+        <v>0.1119519032002793</v>
       </c>
       <c r="N9" t="n">
         <v>1821</v>
@@ -1537,69 +1537,1069 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>2045.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>203.8644157277086</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.7965712665878296</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.07410462791762003</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.7453379467010517</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.07299534777483786</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.7070288067548065</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.07383407280347484</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.6683757210654035</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.07535880398930604</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.8956676568094991</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.003876439338451216</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.908889127474934</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.006880777454275891</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.863632373031453</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.007821318699022049</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.9047695926059749</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.00625828988828591</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.9045095890677143</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.006327084922052311</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.3053123175715119</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.09944092378187683</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8320738773917988</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01009202567273346</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9860746807074998</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01323605724407899</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.996792550439731</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.02729231366164868</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1933</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1926.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>52.75604230796696</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.912556143306958</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.0173956213179226</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.8617358983769104</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.01848491181618573</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.8204781933375118</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.02041860815145606</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.7865687342903215</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.02365482685707256</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.9220854327084155</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.005546661398221416</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9274851707550251</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.005118336229047927</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.8750759052686956</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.01168772652928395</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.9160836170272886</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.009607846144815435</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.9157580748900053</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.00968321174760846</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.1486002239641657</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.01454474402384382</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8320738773917988</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01009202567273346</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.9860746807074998</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01323605724407899</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.996792550439731</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.02729231366164868</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1933</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1926.8</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>52.75604230796696</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.912556143306958</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.0173956213179226</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.8617358983769104</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.01848491181618573</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.8204781933375118</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.02041860815145606</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.7865687342903215</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.02365482685707256</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.9220854327084155</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.005546661398221416</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9274851707550251</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.005118336229047927</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.8750759052686956</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.01168772652928395</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.9160836170272886</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.009607846144815435</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.9157580748900053</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.00968321174760846</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.1901907356948229</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.01449529817795137</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8109046280008465</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.02704788241368848</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9971868140997477</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.006290474906307882</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.027521986549405</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.03561211388012747</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1933</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1986.2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>68.83821613028623</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.879995163970678</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.03116160060338253</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.830680850478695</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.029921247735824</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.7904798347607052</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.02953122084704332</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.757148184514677</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.03008388101686572</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.9129169593357778</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.005549560857646939</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9185022820772157</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.005077558463907992</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8657745078763934</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.003682233818069536</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.9077276191206274</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.003603504582639035</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.9076580813565027</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.004136877555336368</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.1927211646136618</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.04297727327309011</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8109046280008465</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.02704788241368848</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9971868140997477</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.006290474906307882</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.027521986549405</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.03561211388012747</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1933</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1986.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>68.83821613028623</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.879995163970678</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.03116160060338253</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.830680850478695</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.029921247735824</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.7904798347607052</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.02953122084704332</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.757148184514677</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.03008388101686572</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.9129169593357778</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.005549560857646939</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9185022820772157</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.005077558463907992</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8657745078763934</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.003682233818069536</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.9077276191206274</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.003603504582639035</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.9076580813565027</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.004136877555336368</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.2323705722070844</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.04136954126566399</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8250557353750306</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.0108734106249245</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.9882611329385342</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.01955781620400904</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.9886051619989017</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.01926656891498832</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1821</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1800.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>35.08442199419378</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.9059766344845758</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.009287812376401347</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.8531646788384718</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.008133792415239963</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.813520449069688</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.008863268746724388</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.7729454836544</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.009516599464614892</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.9137960132340278</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.003222770662101531</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9279756575866204</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.002726006589007379</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8863700984542131</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.001736331372792155</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.9237485387686368</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.002137550009921369</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.9234456618158194</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.001876348927294145</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.1579264617239301</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.003843907267371714</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8247626307860454</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.009439430356969971</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.9906089063508274</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.01773249364809425</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.9935200439319056</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.01997951026411396</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1821</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1809.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>36.38268819095148</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.9035346951215359</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.009721776242963135</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.8503971723051162</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.009376267719700286</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.8112655170848209</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.009183775963043664</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.7712578714039517</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.009064459419443846</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.913551651037633</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.002843985314749591</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9271125527039052</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.003049276001826901</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8843957665518658</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.004663803949593002</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.9223744675285264</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.00358708780184999</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.9222233944121946</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.003179654384133185</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.2037361354349095</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.00580844972041226</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8192814030233995</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.01247648848990439</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9819125624292745</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0252031656696641</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.9938495332235036</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.03726208433699708</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1821</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>1809.8</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q16" t="n">
         <v>67.85425557767176</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R16" t="n">
         <v>0.9005913783012467</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S16" t="n">
         <v>0.02943620063723383</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T16" t="n">
         <v>0.850900853631449</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U16" t="n">
         <v>0.0287185593420482</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V16" t="n">
         <v>0.8146661846747735</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W16" t="n">
         <v>0.02969977673458377</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X16" t="n">
         <v>0.7784665883757202</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y16" t="n">
         <v>0.03088965888839629</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z16" t="n">
         <v>0.9104244512717476</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA16" t="n">
         <v>0.007556337329172617</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AB16" t="n">
         <v>0.9258008696292567</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AC16" t="n">
         <v>0.00581648641956653</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AD16" t="n">
         <v>0.8823264772716908</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AE16" t="n">
         <v>0.007233991165855591</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AF16" t="n">
         <v>0.9212422337195283</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AG16" t="n">
         <v>0.006524887031671313</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AH16" t="n">
         <v>0.9212780377096174</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AI16" t="n">
         <v>0.006273841921794771</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AJ16" t="n">
+        <v>0.1731163351416516</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.03293368523889948</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8192814030233995</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.01247648848990439</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9819125624292745</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0252031656696641</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.9938495332235036</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.03726208433699708</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1821</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1809.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>67.85425557767176</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.9005913783012467</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.02943620063723383</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.850900853631449</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.0287185593420482</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.8146661846747735</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.02969977673458377</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.7784665883757202</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.03088965888839629</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.9104244512717476</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.007556337329172617</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9258008696292567</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.00581648641956653</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8823264772716908</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.007233991165855591</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.9212422337195283</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.006524887031671313</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.9212780377096174</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.006273841921794771</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>0.2168126094570928</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AK17" t="n">
         <v>0.03165202716739848</v>
       </c>
     </row>

--- a/analysis/aggregate/generative.xlsx
+++ b/analysis/aggregate/generative.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,22 +638,22 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8273050431713951</v>
+        <v>0.817882952469461</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001359001240486718</v>
+        <v>0.03336075437613077</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9872337263398052</v>
+        <v>0.9948728423812749</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01267520072742623</v>
+        <v>0.01061773166307223</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9901707190894982</v>
+        <v>1.012726332126229</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01610386178610805</v>
+        <v>0.03626963297333029</v>
       </c>
       <c r="N2" t="n">
         <v>1933</v>
@@ -662,70 +662,70 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1914</v>
+        <v>1957.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.12876483254676</v>
+        <v>70.10920053744728</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9092920270213792</v>
+        <v>0.889684554113165</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007513307439838513</v>
+        <v>0.03665253595048303</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8568997395190447</v>
+        <v>0.840412883663862</v>
       </c>
       <c r="U2" t="n">
-        <v>0.008916819924062703</v>
+        <v>0.03760248462689449</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8139163539932989</v>
+        <v>0.8000291741191103</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01078799855945918</v>
+        <v>0.03810903751344642</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7780001021324648</v>
+        <v>0.7642703473172275</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01121872197866065</v>
+        <v>0.03771368392978396</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.9142593844753788</v>
+        <v>0.9170884834578577</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003530232510772202</v>
+        <v>0.006694152455158263</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9206323233498352</v>
+        <v>0.9221518104286837</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.001177386710212972</v>
+        <v>0.005380071327327069</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.8665283297092273</v>
+        <v>0.8722208933099875</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.005488937729954532</v>
+        <v>0.008421031402828485</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.9056319126364961</v>
+        <v>0.9105952291482954</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.002998075147592713</v>
+        <v>0.00835144804504309</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.9058122432164868</v>
+        <v>0.910752624697573</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.003523880918820118</v>
+        <v>0.007785820998551203</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1645776566757493</v>
+        <v>0.1835422343324251</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.004687915676862473</v>
+        <v>0.04902270094252971</v>
       </c>
     </row>
     <row r="3">
@@ -746,27 +746,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7450522073408006</v>
+        <v>0.7660399146684428</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08822614134945737</v>
+        <v>0.06244748789220855</v>
       </c>
       <c r="J3" t="n">
         <v>0.998858628268712</v>
@@ -775,10 +775,10 @@
         <v>0.002552184778756518</v>
       </c>
       <c r="L3" t="n">
-        <v>1.069218830832902</v>
+        <v>1.081117434040352</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1393682229968414</v>
+        <v>0.07888689095267745</v>
       </c>
       <c r="N3" t="n">
         <v>1933</v>
@@ -787,70 +787,70 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2066.8</v>
+        <v>2089.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>269.3987750528945</v>
+        <v>152.4883602115256</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8198353862422942</v>
+        <v>0.834896854310944</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09213705341683857</v>
+        <v>0.06532747192420749</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7650798905192053</v>
+        <v>0.7857721453146924</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08867937435664459</v>
+        <v>0.06418538259901294</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7208009298746269</v>
+        <v>0.7444829144179659</v>
       </c>
       <c r="W3" t="n">
-        <v>0.08692992720120768</v>
+        <v>0.06282225351695235</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6848953933455436</v>
+        <v>0.708584727028318</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08696622961631495</v>
+        <v>0.06228057861936535</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.8848227512444622</v>
+        <v>0.9089400143968618</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00851676324074924</v>
+        <v>0.007920364521786408</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8883611644077352</v>
+        <v>0.9142077799003756</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.006713807418121349</v>
+        <v>0.004041873022102839</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.832167664249025</v>
+        <v>0.8630998899287764</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.005528753652546485</v>
+        <v>0.005244352429495055</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.8772194507083941</v>
+        <v>0.9015840360811026</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.006673609034999576</v>
+        <v>0.00364963782483999</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.8771118075857924</v>
+        <v>0.9018609108719293</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.007132392395928331</v>
+        <v>0.002902547504241652</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.300708446866485</v>
+        <v>0.2595095367847411</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.1505638342440073</v>
+        <v>0.09630786239800479</v>
       </c>
     </row>
     <row r="4">
@@ -876,7 +876,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -888,22 +888,22 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7414734126140788</v>
+        <v>0.8181210686384581</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08516716281816633</v>
+        <v>0.003420622468415223</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9966699471786515</v>
+        <v>0.9815012387757294</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005864927705790115</v>
+        <v>0.0176070344418815</v>
       </c>
       <c r="L4" t="n">
-        <v>1.111226073460941</v>
+        <v>0.9879979306777031</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1190838348355368</v>
+        <v>0.02595793472020858</v>
       </c>
       <c r="N4" t="n">
         <v>1933</v>
@@ -912,70 +912,70 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2148</v>
+        <v>1909.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>230.1890527370926</v>
+        <v>50.17668781416326</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8162152670624769</v>
+        <v>0.9061606736099282</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08936555044892601</v>
+        <v>0.01502112037383554</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7638228301397516</v>
+        <v>0.85277133457765</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08761801795640609</v>
+        <v>0.01615513810896959</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7203569661370154</v>
+        <v>0.8090319860864014</v>
       </c>
       <c r="W4" t="n">
-        <v>0.08856151321571945</v>
+        <v>0.0177858880662156</v>
       </c>
       <c r="X4" t="n">
-        <v>0.683360724197301</v>
+        <v>0.7731034442879364</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08970778560051847</v>
+        <v>0.02097853425481329</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.9058587892913437</v>
+        <v>0.9127603768689723</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003270465643860577</v>
+        <v>0.004417373525709362</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9120778912904985</v>
+        <v>0.9195445054255835</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.004847917413308645</v>
+        <v>0.003940011505793553</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.8560359647917398</v>
+        <v>0.8644637111880191</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.008777597652145013</v>
+        <v>0.007116899788490681</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.8956666692736548</v>
+        <v>0.9069561136204678</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.003499724430312057</v>
+        <v>0.005599616446413363</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.8952761436987966</v>
+        <v>0.9071085919314277</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.003811408397708238</v>
+        <v>0.00555359619713808</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.2974386920980926</v>
+        <v>0.1676294277929155</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.122899701614933</v>
+        <v>0.01326278708576599</v>
       </c>
     </row>
     <row r="5">
@@ -1006,17 +1006,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5931048379085917</v>
+        <v>0.7426691185062055</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1040777911348678</v>
+        <v>0.09684680381603999</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1025,10 +1025,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.327263321262287</v>
+        <v>1.122296947749612</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1863261421727778</v>
+        <v>0.1392179733544984</v>
       </c>
       <c r="N5" t="n">
         <v>1933</v>
@@ -1037,70 +1037,70 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2565.6</v>
+        <v>2169.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>360.1684328199794</v>
+        <v>269.1083424942452</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6647619596005004</v>
+        <v>0.8145614885710515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1092326906763957</v>
+        <v>0.0972464979304524</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6128835134007172</v>
+        <v>0.7626017825912214</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1046442583410037</v>
+        <v>0.09641526157872775</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5694837978844337</v>
+        <v>0.718882608583016</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1017689152726394</v>
+        <v>0.09692145840315278</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5334102651105512</v>
+        <v>0.6813244180414256</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1004580910478371</v>
+        <v>0.09603965732762364</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8730149123517306</v>
+        <v>0.9105227817204712</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004256074176362457</v>
+        <v>0.009977470908993018</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8751195797987081</v>
+        <v>0.9145745755750063</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.005736440199221121</v>
+        <v>0.009164397679501682</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.8183687234831118</v>
+        <v>0.8589734998963798</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.007457000263668703</v>
+        <v>0.01056973254109274</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.8632866885403701</v>
+        <v>0.8988129270750763</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.005313885205157843</v>
+        <v>0.006332698568945308</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.8627470325682547</v>
+        <v>0.898685789121733</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.006129075686788877</v>
+        <v>0.0061525652054482</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.5740599455040872</v>
+        <v>0.2971117166212534</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1921317534811748</v>
+        <v>0.152889640671566</v>
       </c>
     </row>
     <row r="6">
@@ -1138,22 +1138,22 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8115676584375976</v>
+        <v>0.8150453088591302</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0106426093157776</v>
+        <v>0.01355271210741352</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9719346695365931</v>
+        <v>0.9806329827639015</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0172217002678691</v>
+        <v>0.02180479158019972</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9724327292696321</v>
+        <v>0.9809994508511807</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01668093209804034</v>
+        <v>0.02125283973780127</v>
       </c>
       <c r="N6" t="n">
         <v>1821</v>
@@ -1162,70 +1162,70 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1770.8</v>
+        <v>1786.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>30.37597735053145</v>
+        <v>38.70142116253613</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9088499987062149</v>
+        <v>0.9061751409778281</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009478603631717965</v>
+        <v>0.007278924547181762</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8541556997567602</v>
+        <v>0.8509483788529885</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01069517908374172</v>
+        <v>0.006605439776116702</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8125478518170303</v>
+        <v>0.8087117508613675</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01346982386077339</v>
+        <v>0.007409440757176325</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7711799997827675</v>
+        <v>0.7655969503427393</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01731052085004423</v>
+        <v>0.007893615478524589</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9055050340135764</v>
+        <v>0.9075900701811681</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00514980577380493</v>
+        <v>0.007366047751125514</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9236217315105855</v>
+        <v>0.9239683105374642</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.00325521436228356</v>
+        <v>0.00468577326477861</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.8785295698344179</v>
+        <v>0.8777529450546069</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.004782441792097627</v>
+        <v>0.006760561398655723</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.9180661053828171</v>
+        <v>0.9180804692328517</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.002290486151917888</v>
+        <v>0.005115630880505663</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.9183449255894287</v>
+        <v>0.9182008966722538</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.002857883711751393</v>
+        <v>0.004905820301228655</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1617046117921775</v>
+        <v>0.1600700525394045</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.006094749859258926</v>
+        <v>0.009038089841683196</v>
       </c>
     </row>
     <row r="7">
@@ -1251,34 +1251,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8115676584375976</v>
+        <v>0.7588931647148504</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0106426093157776</v>
+        <v>0.02922809954717938</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9719346695365931</v>
+        <v>0.9934139460014061</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0172217002678691</v>
+        <v>0.01472686444434023</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9724327292696321</v>
+        <v>1.056232839099396</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01668093209804034</v>
+        <v>0.05228981101118763</v>
       </c>
       <c r="N7" t="n">
         <v>1821</v>
@@ -1287,70 +1287,70 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1770.8</v>
+        <v>1923.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>30.37597735053145</v>
+        <v>95.21974585137265</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9088499987062149</v>
+        <v>0.8357857164441524</v>
       </c>
       <c r="S7" t="n">
-        <v>0.009478603631717965</v>
+        <v>0.03929468878790982</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8541556997567602</v>
+        <v>0.7833368153839666</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01069517908374172</v>
+        <v>0.03870439399865833</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8125478518170303</v>
+        <v>0.7428069740718541</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01346982386077339</v>
+        <v>0.03977153267004557</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7711799997827675</v>
+        <v>0.7018860056328156</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01731052085004423</v>
+        <v>0.0409737665409757</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.9055050340135764</v>
+        <v>0.8977748143496875</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00514980577380493</v>
+        <v>0.004220102760587614</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9236217315105855</v>
+        <v>0.9153071877443463</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.00325521436228356</v>
+        <v>0.004219451843681004</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.8785295698344179</v>
+        <v>0.8691480768884723</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.004782441792097627</v>
+        <v>0.00462582880125925</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.9180661053828171</v>
+        <v>0.9101259999082864</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.002290486151917888</v>
+        <v>0.004360083376258836</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.9183449255894287</v>
+        <v>0.9102119834130526</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.002857883711751393</v>
+        <v>0.003637726642828955</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1617046117921775</v>
+        <v>0.2562755399883246</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.006094749859258926</v>
+        <v>0.04679828015544694</v>
       </c>
     </row>
     <row r="8">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1388,22 +1388,22 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7250156239711663</v>
+        <v>0.8110655816482634</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0695254530698281</v>
+        <v>0.01262462317274522</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9966778178954613</v>
+        <v>0.9779752534944489</v>
       </c>
       <c r="K8" t="n">
-        <v>0.007428625019381896</v>
+        <v>0.01017557695012699</v>
       </c>
       <c r="L8" t="n">
-        <v>1.123448654585393</v>
+        <v>0.9782537067545304</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1119519032002793</v>
+        <v>0.009919701211693067</v>
       </c>
       <c r="N8" t="n">
         <v>1821</v>
@@ -1412,70 +1412,70 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2045.8</v>
+        <v>1781.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>203.8644157277086</v>
+        <v>18.06377590649308</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7965712665878296</v>
+        <v>0.9032371069996528</v>
       </c>
       <c r="S8" t="n">
-        <v>0.07410462791762003</v>
+        <v>0.003086349786243059</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7453379467010517</v>
+        <v>0.8476011661957882</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07299534777483786</v>
+        <v>0.00338287725855128</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7070288067548065</v>
+        <v>0.806883005786343</v>
       </c>
       <c r="W8" t="n">
-        <v>0.07383407280347484</v>
+        <v>0.006801624832933546</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6683757210654035</v>
+        <v>0.765706396253196</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.07535880398930604</v>
+        <v>0.01022072050925863</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.8956676568094991</v>
+        <v>0.9039740482526042</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003876439338451216</v>
+        <v>0.00481794858495362</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.908889127474934</v>
+        <v>0.9210378767316356</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.006880777454275891</v>
+        <v>0.004453505593771836</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.863632373031453</v>
+        <v>0.8746228179192256</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.007821318699022049</v>
+        <v>0.006747597535418517</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.9047695926059749</v>
+        <v>0.9153838643995298</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.00625828988828591</v>
+        <v>0.005028208396266693</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.9045095890677143</v>
+        <v>0.9158016197578454</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.006327084922052311</v>
+        <v>0.004829343810219105</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.3053123175715119</v>
+        <v>0.1666082895504962</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.09944092378187683</v>
+        <v>0.00572869605386905</v>
       </c>
     </row>
     <row r="9">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1506,29 +1506,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7250156239711663</v>
+        <v>0.7203569843567628</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0695254530698281</v>
+        <v>0.1216347395931934</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9966778178954613</v>
+        <v>0.9896361845891704</v>
       </c>
       <c r="K9" t="n">
-        <v>0.007428625019381896</v>
+        <v>0.02317419576487494</v>
       </c>
       <c r="L9" t="n">
-        <v>1.123448654585393</v>
+        <v>1.131466227347611</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1119519032002793</v>
+        <v>0.2077226093129708</v>
       </c>
       <c r="N9" t="n">
         <v>1821</v>
@@ -1537,70 +1537,70 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2045.8</v>
+        <v>2060.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>203.8644157277086</v>
+        <v>378.26287155892</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7965712665878296</v>
+        <v>0.7962178665467141</v>
       </c>
       <c r="S9" t="n">
-        <v>0.07410462791762003</v>
+        <v>0.1290985989536013</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7453379467010517</v>
+        <v>0.7467262163187283</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07299534777483786</v>
+        <v>0.129721091647105</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7070288067548065</v>
+        <v>0.7090668512920916</v>
       </c>
       <c r="W9" t="n">
-        <v>0.07383407280347484</v>
+        <v>0.1320110921855642</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6683757210654035</v>
+        <v>0.6712589874300126</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.07535880398930604</v>
+        <v>0.1346718688685692</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8956676568094991</v>
+        <v>0.8921731517958342</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003876439338451216</v>
+        <v>0.01249583757553294</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.908889127474934</v>
+        <v>0.9071466872348868</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.006880777454275891</v>
+        <v>0.01446334582270776</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.863632373031453</v>
+        <v>0.8621518693601429</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.007821318699022049</v>
+        <v>0.01692556998010173</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.9047695926059749</v>
+        <v>0.9020803981601743</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.00625828988828591</v>
+        <v>0.01521113152985738</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.9045095890677143</v>
+        <v>0.9023356273119753</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.006327084922052311</v>
+        <v>0.01467553053730018</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.3053123175715119</v>
+        <v>0.3384705195563339</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.09944092378187683</v>
+        <v>0.2144655598688916</v>
       </c>
     </row>
     <row r="10">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1638,22 +1638,22 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8320738773917988</v>
+        <v>0.8164108083124505</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01009202567273346</v>
+        <v>0.0220741698201882</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9860746807074998</v>
+        <v>0.9741168578006854</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01323605724407899</v>
+        <v>0.05335164960387338</v>
       </c>
       <c r="L10" t="n">
-        <v>0.996792550439731</v>
+        <v>0.9902741852043455</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02729231366164868</v>
+        <v>0.06121728126972548</v>
       </c>
       <c r="N10" t="n">
         <v>1933</v>
@@ -1662,70 +1662,70 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1926.8</v>
+        <v>1914.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>52.75604230796696</v>
+        <v>118.3330046943794</v>
       </c>
       <c r="R10" t="n">
-        <v>0.912556143306958</v>
+        <v>0.9094531781558258</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0173956213179226</v>
+        <v>0.03358191957546519</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8617358983769104</v>
+        <v>0.8588536427526033</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01848491181618573</v>
+        <v>0.03337985996068617</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8204781933375118</v>
+        <v>0.8159497832516875</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02041860815145606</v>
+        <v>0.03458926518430732</v>
       </c>
       <c r="X10" t="n">
-        <v>0.7865687342903215</v>
+        <v>0.7792434358519879</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02365482685707256</v>
+        <v>0.03601404269140372</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.9220854327084155</v>
+        <v>0.9186807359413353</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.005546661398221416</v>
+        <v>0.01161794726146697</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9274851707550251</v>
+        <v>0.924081199005602</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.005118336229047927</v>
+        <v>0.006837226508140146</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.8750759052686956</v>
+        <v>0.8747037213198489</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.01168772652928395</v>
+        <v>0.0051096535616437</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.9160836170272886</v>
+        <v>0.9127429380013968</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.009607846144815435</v>
+        <v>0.007326939843573979</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.9157580748900053</v>
+        <v>0.9123668049658523</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.00968321174760846</v>
+        <v>0.007270558279867439</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.1486002239641657</v>
+        <v>0.1608062709966405</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.01454474402384382</v>
+        <v>0.01984090568068985</v>
       </c>
     </row>
     <row r="11">
@@ -1746,39 +1746,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8320738773917988</v>
+        <v>0.7858154342206681</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01009202567273346</v>
+        <v>0.0374087769333773</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9860746807074998</v>
+        <v>0.9895990107032846</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01323605724407899</v>
+        <v>0.02325731910070351</v>
       </c>
       <c r="L11" t="n">
-        <v>0.996792550439731</v>
+        <v>1.057630625969995</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02729231366164868</v>
+        <v>0.07181174506916888</v>
       </c>
       <c r="N11" t="n">
         <v>1933</v>
@@ -1787,70 +1787,70 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1926.8</v>
+        <v>2044.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>52.75604230796696</v>
+        <v>138.8121032187036</v>
       </c>
       <c r="R11" t="n">
-        <v>0.912556143306958</v>
+        <v>0.8632278828941942</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0173956213179226</v>
+        <v>0.0490661744904228</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8617358983769104</v>
+        <v>0.8135773439016745</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01848491181618573</v>
+        <v>0.04933339308506313</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8204781933375118</v>
+        <v>0.7717498464781842</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02041860815145606</v>
+        <v>0.05075862537869235</v>
       </c>
       <c r="X11" t="n">
-        <v>0.7865687342903215</v>
+        <v>0.7363873624359945</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02365482685707256</v>
+        <v>0.05393709307356178</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.9220854327084155</v>
+        <v>0.9171030154455956</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.005546661398221416</v>
+        <v>0.009135168346486328</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9274851707550251</v>
+        <v>0.9182517776676871</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.005118336229047927</v>
+        <v>0.008059854934474727</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.8750759052686956</v>
+        <v>0.8653212866598213</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.01168772652928395</v>
+        <v>0.007044172073013604</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.9160836170272886</v>
+        <v>0.905909087293114</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.009607846144815435</v>
+        <v>0.005050269247269533</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.9157580748900053</v>
+        <v>0.9060405235607375</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.00968321174760846</v>
+        <v>0.004891532077395846</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1901907356948229</v>
+        <v>0.2120940649496081</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.01449529817795137</v>
+        <v>0.05191852155515031</v>
       </c>
     </row>
     <row r="12">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1888,22 +1888,22 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8109046280008465</v>
+        <v>0.833810213406724</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02704788241368848</v>
+        <v>0.004622222862952761</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9971868140997477</v>
+        <v>0.9902713176275159</v>
       </c>
       <c r="K12" t="n">
-        <v>0.006290474906307882</v>
+        <v>0.01232770822403719</v>
       </c>
       <c r="L12" t="n">
-        <v>1.027521986549405</v>
+        <v>0.9915157785825143</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03561211388012747</v>
+        <v>0.01343367155345418</v>
       </c>
       <c r="N12" t="n">
         <v>1933</v>
@@ -1912,70 +1912,70 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1986.2</v>
+        <v>1916.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>68.83821613028623</v>
+        <v>25.96728711282715</v>
       </c>
       <c r="R12" t="n">
-        <v>0.879995163970678</v>
+        <v>0.9115161063603413</v>
       </c>
       <c r="S12" t="n">
-        <v>0.03116160060338253</v>
+        <v>0.0107996457368836</v>
       </c>
       <c r="T12" t="n">
-        <v>0.830680850478695</v>
+        <v>0.8600067192919545</v>
       </c>
       <c r="U12" t="n">
-        <v>0.029921247735824</v>
+        <v>0.01169403843669491</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7904798347607052</v>
+        <v>0.8182385934020846</v>
       </c>
       <c r="W12" t="n">
-        <v>0.02953122084704332</v>
+        <v>0.01134980598859879</v>
       </c>
       <c r="X12" t="n">
-        <v>0.757148184514677</v>
+        <v>0.7840124306553514</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.03008388101686572</v>
+        <v>0.01194408235819456</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.9129169593357778</v>
+        <v>0.9210687582985134</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.005549560857646939</v>
+        <v>0.003432094191594611</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9185022820772157</v>
+        <v>0.9266610371009648</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.005077558463907992</v>
+        <v>0.005021602510288775</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.8657745078763934</v>
+        <v>0.8723072986394442</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.003682233818069536</v>
+        <v>0.008325222461903131</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.9077276191206274</v>
+        <v>0.9149436443734287</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.003603504582639035</v>
+        <v>0.00445960975038454</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.9076580813565027</v>
+        <v>0.9151143946765494</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.004136877555336368</v>
+        <v>0.004397606422658104</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1927211646136618</v>
+        <v>0.1535274356103024</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.04297727327309011</v>
+        <v>0.01049290640548486</v>
       </c>
     </row>
     <row r="13">
@@ -2006,29 +2006,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8109046280008465</v>
+        <v>0.8004607184574544</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02704788241368848</v>
+        <v>0.04006244200412974</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9971868140997477</v>
+        <v>0.998858628268712</v>
       </c>
       <c r="K13" t="n">
-        <v>0.006290474906307882</v>
+        <v>0.002552184778756508</v>
       </c>
       <c r="L13" t="n">
-        <v>1.027521986549405</v>
+        <v>1.048422141748577</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03561211388012747</v>
+        <v>0.04633589919173205</v>
       </c>
       <c r="N13" t="n">
         <v>1933</v>
@@ -2037,70 +2037,70 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1986.2</v>
+        <v>2026.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>68.83821613028623</v>
+        <v>89.56729313761807</v>
       </c>
       <c r="R13" t="n">
-        <v>0.879995163970678</v>
+        <v>0.8689425744789346</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03116160060338253</v>
+        <v>0.03972299612902561</v>
       </c>
       <c r="T13" t="n">
-        <v>0.830680850478695</v>
+        <v>0.8196198158036442</v>
       </c>
       <c r="U13" t="n">
-        <v>0.029921247735824</v>
+        <v>0.04062582766322528</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7904798347607052</v>
+        <v>0.7785265199706124</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02953122084704332</v>
+        <v>0.04208204790937348</v>
       </c>
       <c r="X13" t="n">
-        <v>0.757148184514677</v>
+        <v>0.7440771288936261</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.03008388101686572</v>
+        <v>0.04351396596737222</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.9129169593357778</v>
+        <v>0.9159085592172003</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.005549560857646939</v>
+        <v>0.01090754558670793</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9185022820772157</v>
+        <v>0.9185253446979044</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.005077558463907992</v>
+        <v>0.01012037948218936</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.8657745078763934</v>
+        <v>0.8655688658330579</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.003682233818069536</v>
+        <v>0.01178609333011801</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.9077276191206274</v>
+        <v>0.9081230077310884</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.003603504582639035</v>
+        <v>0.0108539618808168</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.9076580813565027</v>
+        <v>0.9081453974565292</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.004136877555336368</v>
+        <v>0.01104510899289124</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.2323705722070844</v>
+        <v>0.203023516237402</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.04136954126566399</v>
+        <v>0.05351993837678199</v>
       </c>
     </row>
     <row r="14">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2135,25 +2135,25 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8250557353750306</v>
+        <v>0.8290445635266337</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0108734106249245</v>
+        <v>0.0144127242152091</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9882611329385342</v>
+        <v>0.9895032678343227</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01955781620400904</v>
+        <v>0.004572331138164055</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9886051619989017</v>
+        <v>0.9895661724327294</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01926656891498832</v>
+        <v>0.004528397172561965</v>
       </c>
       <c r="N14" t="n">
         <v>1821</v>
@@ -2162,70 +2162,70 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1800.25</v>
+        <v>1802</v>
       </c>
       <c r="Q14" t="n">
-        <v>35.08442199419378</v>
+        <v>8.246211251235319</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9059766344845758</v>
+        <v>0.9067518839775148</v>
       </c>
       <c r="S14" t="n">
-        <v>0.009287812376401347</v>
+        <v>0.01092254314775064</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8531646788384718</v>
+        <v>0.8556577778871404</v>
       </c>
       <c r="U14" t="n">
-        <v>0.008133792415239963</v>
+        <v>0.01180795544544077</v>
       </c>
       <c r="V14" t="n">
-        <v>0.813520449069688</v>
+        <v>0.8172787233361614</v>
       </c>
       <c r="W14" t="n">
-        <v>0.008863268746724388</v>
+        <v>0.01291507394140667</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7729454836544</v>
+        <v>0.77703597370956</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.009516599464614892</v>
+        <v>0.01337189553049761</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.9137960132340278</v>
+        <v>0.9127662141060015</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.003222770662101531</v>
+        <v>0.01049916765032839</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9279756575866204</v>
+        <v>0.9273600484951128</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.002726006589007379</v>
+        <v>0.009162342451410203</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.8863700984542131</v>
+        <v>0.8869215667377592</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.001736331372792155</v>
+        <v>0.01115586733378617</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.9237485387686368</v>
+        <v>0.92359879070787</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.002137550009921369</v>
+        <v>0.01009738050030383</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.9234456618158194</v>
+        <v>0.9235074306569947</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.001876348927294145</v>
+        <v>0.009980971549724715</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.1579264617239301</v>
+        <v>0.1549125979505726</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.003843907267371714</v>
+        <v>0.02169144570879636</v>
       </c>
     </row>
     <row r="15">
@@ -2246,39 +2246,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8247626307860454</v>
+        <v>0.8126737439334647</v>
       </c>
       <c r="I15" t="n">
-        <v>0.009439430356969971</v>
+        <v>0.01458800372760369</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9906089063508274</v>
+        <v>0.9962307113043432</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01773249364809425</v>
+        <v>0.008428385750310234</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9935200439319056</v>
+        <v>1.019659527732015</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01997951026411396</v>
+        <v>0.02712706235049778</v>
       </c>
       <c r="N15" t="n">
         <v>1821</v>
@@ -2287,70 +2287,70 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1809.2</v>
+        <v>1856.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>36.38268819095148</v>
+        <v>49.39838054025658</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9035346951215359</v>
+        <v>0.885578799350802</v>
       </c>
       <c r="S15" t="n">
-        <v>0.009721776242963135</v>
+        <v>0.01928029743415816</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8503971723051162</v>
+        <v>0.8332037861636902</v>
       </c>
       <c r="U15" t="n">
-        <v>0.009376267719700286</v>
+        <v>0.01792837808971346</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8112655170848209</v>
+        <v>0.7944429761437903</v>
       </c>
       <c r="W15" t="n">
-        <v>0.009183775963043664</v>
+        <v>0.01780632844512921</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7712578714039517</v>
+        <v>0.7557260152939287</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.009064459419443846</v>
+        <v>0.01854049765808166</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.913551651037633</v>
+        <v>0.9104258566669884</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.002843985314749591</v>
+        <v>0.004046610816476249</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9271125527039052</v>
+        <v>0.9240710070263383</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.003049276001826901</v>
+        <v>0.003209823230506822</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.8843957665518658</v>
+        <v>0.879791243300439</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.004663803949593002</v>
+        <v>0.003488421120153379</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.9223744675285264</v>
+        <v>0.9195916542247996</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.00358708780184999</v>
+        <v>0.003096639440676179</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.9222233944121946</v>
+        <v>0.9190010725982616</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.003179654384133185</v>
+        <v>0.002967965417189208</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.2037361354349095</v>
+        <v>0.1833634719710669</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.00580844972041226</v>
+        <v>0.02134700796813619</v>
       </c>
     </row>
     <row r="16">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2388,22 +2388,22 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8192814030233995</v>
+        <v>0.8188438350867335</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01247648848990439</v>
+        <v>0.008452741205759543</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9819125624292745</v>
+        <v>0.9631675271728121</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0252031656696641</v>
+        <v>0.02624120293432901</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9938495332235036</v>
+        <v>0.9663920922570016</v>
       </c>
       <c r="M16" t="n">
-        <v>0.03726208433699708</v>
+        <v>0.02959142820333146</v>
       </c>
       <c r="N16" t="n">
         <v>1821</v>
@@ -2412,70 +2412,70 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1809.8</v>
+        <v>1759.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>67.85425557767176</v>
+        <v>53.88599075826664</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9005913783012467</v>
+        <v>0.9202413885024319</v>
       </c>
       <c r="S16" t="n">
-        <v>0.02943620063723383</v>
+        <v>0.01504192594460961</v>
       </c>
       <c r="T16" t="n">
-        <v>0.850900853631449</v>
+        <v>0.8678496069677741</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0287185593420482</v>
+        <v>0.01473472195888493</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8146661846747735</v>
+        <v>0.8291228416459523</v>
       </c>
       <c r="W16" t="n">
-        <v>0.02969977673458377</v>
+        <v>0.01506225983608098</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7784665883757202</v>
+        <v>0.7901213272483382</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.03088965888839629</v>
+        <v>0.01537855368175703</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.9104244512717476</v>
+        <v>0.9123148427768222</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.007556337329172617</v>
+        <v>0.005953896148101475</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9258008696292567</v>
+        <v>0.9290536753499072</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.00581648641956653</v>
+        <v>0.0043934628639202</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.8823264772716908</v>
+        <v>0.8866654715911197</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.007233991165855591</v>
+        <v>0.005254444736708794</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.9212422337195283</v>
+        <v>0.9241323289186697</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.006524887031671313</v>
+        <v>0.005294937835861651</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.9212780377096174</v>
+        <v>0.9240126139457567</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.006273841921794771</v>
+        <v>0.004650719594276509</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.1731163351416516</v>
+        <v>0.151416515973478</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.03293368523889948</v>
+        <v>0.005032340316996219</v>
       </c>
     </row>
     <row r="17">
@@ -2506,29 +2506,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8192814030233995</v>
+        <v>0.8278824579334177</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01247648848990439</v>
+        <v>0.0120725989295183</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9819125624292745</v>
+        <v>0.9807953588997853</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0252031656696641</v>
+        <v>0.02529024805724558</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9938495332235036</v>
+        <v>0.9817682591982427</v>
       </c>
       <c r="M17" t="n">
-        <v>0.03726208433699708</v>
+        <v>0.02503420039942332</v>
       </c>
       <c r="N17" t="n">
         <v>1821</v>
@@ -2537,70 +2537,70 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1809.8</v>
+        <v>1787.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>67.85425557767176</v>
+        <v>45.58727892734991</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9005913783012467</v>
+        <v>0.9121976477768177</v>
       </c>
       <c r="S17" t="n">
-        <v>0.02943620063723383</v>
+        <v>0.02601066912545551</v>
       </c>
       <c r="T17" t="n">
-        <v>0.850900853631449</v>
+        <v>0.8617985861974626</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0287185593420482</v>
+        <v>0.0260135433431228</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8146661846747735</v>
+        <v>0.8234444589293629</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02969977673458377</v>
+        <v>0.02621743815148606</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7784665883757202</v>
+        <v>0.7859828544935417</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.03088965888839629</v>
+        <v>0.02550180475552104</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.9104244512717476</v>
+        <v>0.9120500128538588</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.007556337329172617</v>
+        <v>0.01358613209374317</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9258008696292567</v>
+        <v>0.9288473138677856</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.00581648641956653</v>
+        <v>0.01096499804936921</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.8823264772716908</v>
+        <v>0.8840397481776016</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.007233991165855591</v>
+        <v>0.01337003418310758</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.9212422337195283</v>
+        <v>0.9225985615405092</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.006524887031671313</v>
+        <v>0.01199752465536127</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.9212780377096174</v>
+        <v>0.9226217627814609</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.006273841921794771</v>
+        <v>0.0120437525442844</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.2168126094570928</v>
+        <v>0.1616636528028933</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.03165202716739848</v>
+        <v>0.0365744507351604</v>
       </c>
     </row>
   </sheetData>
